--- a/InterfaceProject/odd_selection_nested_structure.xlsx
+++ b/InterfaceProject/odd_selection_nested_structure.xlsx
@@ -903,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
